--- a/docs/legal-acts/export/EU 2015-1502.xlsx
+++ b/docs/legal-acts/export/EU 2015-1502.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 18:24</t>
+          <t>2026-10-21 18:31</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr"/>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr"/>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr"/>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr"/>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -15472,7 +15472,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -16309,7 +16309,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -17053,7 +17053,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -17425,7 +17425,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -17518,7 +17518,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -17890,7 +17890,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -18262,7 +18262,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -19471,7 +19471,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -19843,7 +19843,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -19936,7 +19936,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
